--- a/outputs/generated/nitro_bioisostere_campaign/mol2mol_scaffold/curriculum_learning/mol2mol_scaffold_cl_generated_optimal.xlsx
+++ b/outputs/generated/nitro_bioisostere_campaign/mol2mol_scaffold/curriculum_learning/mol2mol_scaffold_cl_generated_optimal.xlsx
@@ -2036,7 +2036,7 @@
         <v>0.7651771522401469</v>
       </c>
       <c r="R2" s="3">
-        <v>0.3484761476666539</v>
+        <v>0.3484761476666538</v>
       </c>
       <c r="S2" s="3">
         <v>348.0707217953223</v>
@@ -2051,7 +2051,7 @@
         <v>0.7651771522401469</v>
       </c>
       <c r="W2" s="3">
-        <v>3.466200000000002</v>
+        <v>3.466200000000001</v>
       </c>
       <c r="X2" s="3">
         <v>-5.319363432139666</v>
@@ -2065,13 +2065,13 @@
         </is>
       </c>
       <c r="AA2" s="3">
-        <v>38.25123977661133</v>
+        <v>38.25124</v>
       </c>
       <c r="AB2" s="3">
-        <v>34.25670623779297</v>
+        <v>34.256706</v>
       </c>
       <c r="AC2" s="3">
-        <v>42.6740608215332</v>
+        <v>42.67406</v>
       </c>
       <c r="AD2" s="3">
         <v>0</v>
@@ -2083,64 +2083,64 @@
         <v>0</v>
       </c>
       <c r="AG2" s="3">
-        <v>0.5682803392410278</v>
+        <v>0.5682803400000001</v>
       </c>
       <c r="AH2" s="3">
-        <v>0.2342183887958527</v>
+        <v>0.23421839</v>
       </c>
       <c r="AI2" s="3">
-        <v>0.926491916179657</v>
+        <v>0.9264919</v>
       </c>
       <c r="AJ2" s="3">
-        <v>0.0770404189825058</v>
+        <v>0.07704042</v>
       </c>
       <c r="AK2" s="3">
-        <v>0.8519454002380371</v>
+        <v>0.8519454</v>
       </c>
       <c r="AL2" s="3">
-        <v>0.1560324281454086</v>
+        <v>0.15603243</v>
       </c>
       <c r="AM2" s="3">
-        <v>0.6287150382995605</v>
+        <v>0.62871504</v>
       </c>
       <c r="AN2" s="3">
-        <v>0.753603458404541</v>
+        <v>0.75360346</v>
       </c>
       <c r="AO2" s="3">
-        <v>0.1165525317192078</v>
+        <v>0.11655253</v>
       </c>
       <c r="AP2" s="3">
-        <v>0.9704455137252808</v>
+        <v>0.9704455</v>
       </c>
       <c r="AQ2" s="3">
-        <v>0.9998899698257446</v>
+        <v>0.99988997</v>
       </c>
       <c r="AR2" s="3">
-        <v>0.783534049987793</v>
+        <v>0.78353405</v>
       </c>
       <c r="AS2" s="3">
-        <v>0.95196533203125</v>
+        <v>0.9519653300000001</v>
       </c>
       <c r="AT2" s="3">
-        <v>0.8813806772232056</v>
+        <v>0.8813807</v>
       </c>
       <c r="AU2" s="3">
-        <v>-4.786739826202393</v>
+        <v>-4.78674</v>
       </c>
       <c r="AV2" s="3">
-        <v>98.07588195800781</v>
+        <v>98.07588</v>
       </c>
       <c r="AW2" s="3">
-        <v>7.37607479095459</v>
+        <v>7.376075</v>
       </c>
       <c r="AX2" s="3">
         <v>433.5120000000002</v>
       </c>
       <c r="AY2" s="3">
-        <v>3.466200000000002</v>
+        <v>3.466200000000001</v>
       </c>
       <c r="AZ2" s="3">
-        <v>0.2544738696046526</v>
+        <v>0.2544738696046525</v>
       </c>
       <c r="BA2" s="3">
         <v>4</v>
@@ -2199,7 +2199,7 @@
         <v>5.534869540208962</v>
       </c>
       <c r="L3" s="3">
-        <v>0.9970009323160607</v>
+        <v>0.9970009323160608</v>
       </c>
       <c r="M3" s="3">
         <v>0.592251287607766</v>
@@ -2246,13 +2246,13 @@
         </is>
       </c>
       <c r="AA3" s="3">
-        <v>62.79464721679688</v>
+        <v>62.794647</v>
       </c>
       <c r="AB3" s="3">
-        <v>37.00864410400391</v>
+        <v>37.008644</v>
       </c>
       <c r="AC3" s="3">
-        <v>50.70552444458008</v>
+        <v>50.705524</v>
       </c>
       <c r="AD3" s="3">
         <v>0</v>
@@ -2264,55 +2264,55 @@
         <v>0</v>
       </c>
       <c r="AG3" s="3">
-        <v>0.3520895540714264</v>
+        <v>0.35208955</v>
       </c>
       <c r="AH3" s="3">
-        <v>0.4673394560813904</v>
+        <v>0.46733946</v>
       </c>
       <c r="AI3" s="3">
-        <v>0.8214842081069946</v>
+        <v>0.8214842</v>
       </c>
       <c r="AJ3" s="3">
-        <v>0.2316653430461884</v>
+        <v>0.23166534</v>
       </c>
       <c r="AK3" s="3">
-        <v>0.9373928904533386</v>
+        <v>0.9373929</v>
       </c>
       <c r="AL3" s="3">
-        <v>0.05347534269094467</v>
+        <v>0.053475343</v>
       </c>
       <c r="AM3" s="3">
-        <v>0.4774840474128723</v>
+        <v>0.47748405</v>
       </c>
       <c r="AN3" s="3">
-        <v>0.665554404258728</v>
+        <v>0.6655544</v>
       </c>
       <c r="AO3" s="3">
-        <v>0.4196734428405762</v>
+        <v>0.41967344</v>
       </c>
       <c r="AP3" s="3">
-        <v>0.9703501462936401</v>
+        <v>0.97035015</v>
       </c>
       <c r="AQ3" s="3">
-        <v>0.9991868734359741</v>
+        <v>0.9991869</v>
       </c>
       <c r="AR3" s="3">
-        <v>0.7410286664962769</v>
+        <v>0.7410286699999999</v>
       </c>
       <c r="AS3" s="3">
-        <v>0.8547223210334778</v>
+        <v>0.8547223</v>
       </c>
       <c r="AT3" s="3">
-        <v>0.9185638427734375</v>
+        <v>0.91856384</v>
       </c>
       <c r="AU3" s="3">
-        <v>-4.961644172668457</v>
+        <v>-4.961644</v>
       </c>
       <c r="AV3" s="3">
-        <v>98.92704010009766</v>
+        <v>98.92704000000001</v>
       </c>
       <c r="AW3" s="3">
-        <v>6.640058994293213</v>
+        <v>6.640059</v>
       </c>
       <c r="AX3" s="3">
         <v>511.6480000000003</v>
@@ -2404,7 +2404,7 @@
         <v>278.8545515586202</v>
       </c>
       <c r="T4" s="3">
-        <v>3.554622262412655</v>
+        <v>3.554622262412656</v>
       </c>
       <c r="U4" s="3">
         <v>5.829204178560643</v>
@@ -2427,13 +2427,13 @@
         </is>
       </c>
       <c r="AA4" s="3">
-        <v>23.21879768371582</v>
+        <v>23.218798</v>
       </c>
       <c r="AB4" s="3">
-        <v>26.07429122924805</v>
+        <v>26.074291</v>
       </c>
       <c r="AC4" s="3">
-        <v>42.78295135498047</v>
+        <v>42.78295</v>
       </c>
       <c r="AD4" s="3">
         <v>0</v>
@@ -2445,55 +2445,55 @@
         <v>0</v>
       </c>
       <c r="AG4" s="3">
-        <v>0.1793070733547211</v>
+        <v>0.17930707</v>
       </c>
       <c r="AH4" s="3">
-        <v>0.6316911578178406</v>
+        <v>0.63169116</v>
       </c>
       <c r="AI4" s="3">
-        <v>0.6344317197799683</v>
+        <v>0.6344317</v>
       </c>
       <c r="AJ4" s="3">
-        <v>0.09223625808954239</v>
+        <v>0.09223626</v>
       </c>
       <c r="AK4" s="3">
-        <v>0.9331737756729126</v>
+        <v>0.9331738000000001</v>
       </c>
       <c r="AL4" s="3">
-        <v>0.1351943910121918</v>
+        <v>0.13519439</v>
       </c>
       <c r="AM4" s="3">
-        <v>0.213327556848526</v>
+        <v>0.21332756</v>
       </c>
       <c r="AN4" s="3">
-        <v>0.3550845682621002</v>
+        <v>0.35508457</v>
       </c>
       <c r="AO4" s="3">
-        <v>0.3897414803504944</v>
+        <v>0.38974148</v>
       </c>
       <c r="AP4" s="3">
-        <v>0.8482102155685425</v>
+        <v>0.8482102</v>
       </c>
       <c r="AQ4" s="3">
-        <v>0.9978948831558228</v>
+        <v>0.9978949</v>
       </c>
       <c r="AR4" s="3">
-        <v>0.7498563528060913</v>
+        <v>0.7498563499999999</v>
       </c>
       <c r="AS4" s="3">
-        <v>0.783575713634491</v>
+        <v>0.7835757</v>
       </c>
       <c r="AT4" s="3">
-        <v>0.7166632413864136</v>
+        <v>0.71666324</v>
       </c>
       <c r="AU4" s="3">
-        <v>-5.260924339294434</v>
+        <v>-5.2609243</v>
       </c>
       <c r="AV4" s="3">
-        <v>92.48931884765625</v>
+        <v>92.48932000000001</v>
       </c>
       <c r="AW4" s="3">
-        <v>10.3605432510376</v>
+        <v>10.360543</v>
       </c>
       <c r="AX4" s="3">
         <v>417.5570000000002</v>
@@ -2608,13 +2608,13 @@
         </is>
       </c>
       <c r="AA5" s="3">
-        <v>62.39081573486328</v>
+        <v>62.390816</v>
       </c>
       <c r="AB5" s="3">
-        <v>57.58206176757812</v>
+        <v>57.58206</v>
       </c>
       <c r="AC5" s="3">
-        <v>51.6802978515625</v>
+        <v>51.680298</v>
       </c>
       <c r="AD5" s="3">
         <v>0</v>
@@ -2626,55 +2626,55 @@
         <v>0</v>
       </c>
       <c r="AG5" s="3">
-        <v>0.0497056320309639</v>
+        <v>0.049705632</v>
       </c>
       <c r="AH5" s="3">
-        <v>0.2396424263715744</v>
+        <v>0.23964243</v>
       </c>
       <c r="AI5" s="3">
-        <v>0.8849323391914368</v>
+        <v>0.88493234</v>
       </c>
       <c r="AJ5" s="3">
-        <v>0.08105400204658508</v>
+        <v>0.081054</v>
       </c>
       <c r="AK5" s="3">
-        <v>0.8425236940383911</v>
+        <v>0.8425237</v>
       </c>
       <c r="AL5" s="3">
-        <v>0.2971973419189453</v>
+        <v>0.29719734</v>
       </c>
       <c r="AM5" s="3">
-        <v>0.7376927733421326</v>
+        <v>0.7376928</v>
       </c>
       <c r="AN5" s="3">
-        <v>0.8714698553085327</v>
+        <v>0.87146986</v>
       </c>
       <c r="AO5" s="3">
-        <v>0.1994397193193436</v>
+        <v>0.19943972</v>
       </c>
       <c r="AP5" s="3">
-        <v>0.9584704637527466</v>
+        <v>0.95847046</v>
       </c>
       <c r="AQ5" s="3">
-        <v>0.9998761415481567</v>
+        <v>0.99987614</v>
       </c>
       <c r="AR5" s="3">
-        <v>0.7683823108673096</v>
+        <v>0.7683823</v>
       </c>
       <c r="AS5" s="3">
-        <v>0.9477031826972961</v>
+        <v>0.9477032</v>
       </c>
       <c r="AT5" s="3">
-        <v>0.8606227040290833</v>
+        <v>0.8606227</v>
       </c>
       <c r="AU5" s="3">
-        <v>-4.662340641021729</v>
+        <v>-4.6623406</v>
       </c>
       <c r="AV5" s="3">
-        <v>99.64119720458984</v>
+        <v>99.6412</v>
       </c>
       <c r="AW5" s="3">
-        <v>6.217146873474121</v>
+        <v>6.217147</v>
       </c>
       <c r="AX5" s="3">
         <v>421.4720000000002</v>
@@ -2789,13 +2789,13 @@
         </is>
       </c>
       <c r="AA6" s="3">
-        <v>54.03302001953125</v>
+        <v>54.03302</v>
       </c>
       <c r="AB6" s="3">
-        <v>51.58975982666016</v>
+        <v>51.58976</v>
       </c>
       <c r="AC6" s="3">
-        <v>46.11929321289062</v>
+        <v>46.119293</v>
       </c>
       <c r="AD6" s="3">
         <v>0</v>
@@ -2807,55 +2807,55 @@
         <v>0</v>
       </c>
       <c r="AG6" s="3">
-        <v>0.1514938771724701</v>
+        <v>0.15149388</v>
       </c>
       <c r="AH6" s="3">
-        <v>0.3794129490852356</v>
+        <v>0.37941295</v>
       </c>
       <c r="AI6" s="3">
-        <v>0.790505588054657</v>
+        <v>0.7905056</v>
       </c>
       <c r="AJ6" s="3">
-        <v>0.05281468480825424</v>
+        <v>0.052814685</v>
       </c>
       <c r="AK6" s="3">
-        <v>0.8946078419685364</v>
+        <v>0.89460784</v>
       </c>
       <c r="AL6" s="3">
-        <v>0.4100111424922943</v>
+        <v>0.41001114</v>
       </c>
       <c r="AM6" s="3">
-        <v>0.6163968443870544</v>
+        <v>0.6163968399999999</v>
       </c>
       <c r="AN6" s="3">
-        <v>0.7340325713157654</v>
+        <v>0.7340326</v>
       </c>
       <c r="AO6" s="3">
-        <v>0.2590198218822479</v>
+        <v>0.25901982</v>
       </c>
       <c r="AP6" s="3">
-        <v>0.9837437868118286</v>
+        <v>0.9837437999999999</v>
       </c>
       <c r="AQ6" s="3">
-        <v>0.9999759793281555</v>
+        <v>0.999976</v>
       </c>
       <c r="AR6" s="3">
-        <v>0.7540546655654907</v>
+        <v>0.75405467</v>
       </c>
       <c r="AS6" s="3">
-        <v>0.9556649327278137</v>
+        <v>0.95566493</v>
       </c>
       <c r="AT6" s="3">
-        <v>0.8375112414360046</v>
+        <v>0.83751124</v>
       </c>
       <c r="AU6" s="3">
-        <v>-4.578262329101562</v>
+        <v>-4.5782623</v>
       </c>
       <c r="AV6" s="3">
-        <v>98.41603851318359</v>
+        <v>98.41604</v>
       </c>
       <c r="AW6" s="3">
-        <v>6.461910247802734</v>
+        <v>6.4619102</v>
       </c>
       <c r="AX6" s="3">
         <v>421.4720000000002</v>
@@ -2970,13 +2970,13 @@
         </is>
       </c>
       <c r="AA7" s="3">
-        <v>54.02365875244141</v>
+        <v>54.02366</v>
       </c>
       <c r="AB7" s="3">
-        <v>51.60739898681641</v>
+        <v>51.6074</v>
       </c>
       <c r="AC7" s="3">
-        <v>46.01802825927734</v>
+        <v>46.01803</v>
       </c>
       <c r="AD7" s="3">
         <v>0</v>
@@ -2988,55 +2988,55 @@
         <v>0</v>
       </c>
       <c r="AG7" s="3">
-        <v>0.1515597701072693</v>
+        <v>0.15155977</v>
       </c>
       <c r="AH7" s="3">
-        <v>0.3794240355491638</v>
+        <v>0.37942404</v>
       </c>
       <c r="AI7" s="3">
-        <v>0.7904849052429199</v>
+        <v>0.7904849</v>
       </c>
       <c r="AJ7" s="3">
-        <v>0.0527871660888195</v>
+        <v>0.052787166</v>
       </c>
       <c r="AK7" s="3">
-        <v>0.8945648074150085</v>
+        <v>0.8945648</v>
       </c>
       <c r="AL7" s="3">
-        <v>0.4096334874629974</v>
+        <v>0.4096335</v>
       </c>
       <c r="AM7" s="3">
-        <v>0.6159688234329224</v>
+        <v>0.6159688</v>
       </c>
       <c r="AN7" s="3">
-        <v>0.7336847186088562</v>
+        <v>0.7336847</v>
       </c>
       <c r="AO7" s="3">
-        <v>0.2587462067604065</v>
+        <v>0.2587462</v>
       </c>
       <c r="AP7" s="3">
-        <v>0.9837337732315063</v>
+        <v>0.9837338</v>
       </c>
       <c r="AQ7" s="3">
-        <v>0.9999759793281555</v>
+        <v>0.999976</v>
       </c>
       <c r="AR7" s="3">
-        <v>0.7541525363922119</v>
+        <v>0.75415254</v>
       </c>
       <c r="AS7" s="3">
-        <v>0.955665111541748</v>
+        <v>0.9556651</v>
       </c>
       <c r="AT7" s="3">
-        <v>0.8373624682426453</v>
+        <v>0.83736247</v>
       </c>
       <c r="AU7" s="3">
-        <v>-4.578091621398926</v>
+        <v>-4.5780916</v>
       </c>
       <c r="AV7" s="3">
-        <v>98.40773010253906</v>
+        <v>98.40773</v>
       </c>
       <c r="AW7" s="3">
-        <v>6.452359199523926</v>
+        <v>6.452359</v>
       </c>
       <c r="AX7" s="3">
         <v>420.4749380000002</v>
@@ -3151,13 +3151,13 @@
         </is>
       </c>
       <c r="AA8" s="3">
-        <v>49.53058624267578</v>
+        <v>49.530586</v>
       </c>
       <c r="AB8" s="3">
-        <v>50.50267791748047</v>
+        <v>50.502678</v>
       </c>
       <c r="AC8" s="3">
-        <v>42.52789688110352</v>
+        <v>42.527897</v>
       </c>
       <c r="AD8" s="3">
         <v>0</v>
@@ -3169,55 +3169,55 @@
         <v>0</v>
       </c>
       <c r="AG8" s="3">
-        <v>0.1503766626119614</v>
+        <v>0.15037666</v>
       </c>
       <c r="AH8" s="3">
-        <v>0.4014430642127991</v>
+        <v>0.40144306</v>
       </c>
       <c r="AI8" s="3">
-        <v>0.7944496870040894</v>
+        <v>0.7944497</v>
       </c>
       <c r="AJ8" s="3">
-        <v>0.06801829487085342</v>
+        <v>0.06801829500000001</v>
       </c>
       <c r="AK8" s="3">
-        <v>0.9175645112991333</v>
+        <v>0.9175645</v>
       </c>
       <c r="AL8" s="3">
-        <v>0.4286567568778992</v>
+        <v>0.42865676</v>
       </c>
       <c r="AM8" s="3">
-        <v>0.7177208662033081</v>
+        <v>0.71772087</v>
       </c>
       <c r="AN8" s="3">
-        <v>0.8529923558235168</v>
+        <v>0.85299236</v>
       </c>
       <c r="AO8" s="3">
-        <v>0.3775244355201721</v>
+        <v>0.37752444</v>
       </c>
       <c r="AP8" s="3">
-        <v>0.9936367273330688</v>
+        <v>0.9936367</v>
       </c>
       <c r="AQ8" s="3">
-        <v>0.9999710321426392</v>
+        <v>0.99997103</v>
       </c>
       <c r="AR8" s="3">
-        <v>0.653423011302948</v>
+        <v>0.653423</v>
       </c>
       <c r="AS8" s="3">
-        <v>0.936070442199707</v>
+        <v>0.9360704399999999</v>
       </c>
       <c r="AT8" s="3">
-        <v>0.899492084980011</v>
+        <v>0.8994921</v>
       </c>
       <c r="AU8" s="3">
-        <v>-4.60943078994751</v>
+        <v>-4.609431</v>
       </c>
       <c r="AV8" s="3">
-        <v>99.28874969482422</v>
+        <v>99.28874999999999</v>
       </c>
       <c r="AW8" s="3">
-        <v>4.949751853942871</v>
+        <v>4.949752</v>
       </c>
       <c r="AX8" s="3">
         <v>445.4940000000003</v>
@@ -3232,7 +3232,7 @@
         <v>4</v>
       </c>
       <c r="BB8" s="3">
-        <v>3.712554966519908</v>
+        <v>3.712554966519909</v>
       </c>
       <c r="BC8" s="3">
         <v>0.6986050037200102</v>
@@ -3285,7 +3285,7 @@
         <v>5.442375258869468</v>
       </c>
       <c r="L9" s="3">
-        <v>0.9042563426665993</v>
+        <v>0.9042563426665992</v>
       </c>
       <c r="M9" s="3">
         <v>0.2814547288330222</v>
@@ -3332,13 +3332,13 @@
         </is>
       </c>
       <c r="AA9" s="3">
-        <v>62.37113189697266</v>
+        <v>62.37113</v>
       </c>
       <c r="AB9" s="3">
-        <v>55.22407150268555</v>
+        <v>55.22407</v>
       </c>
       <c r="AC9" s="3">
-        <v>42.2302131652832</v>
+        <v>42.230213</v>
       </c>
       <c r="AD9" s="3">
         <v>0</v>
@@ -3350,55 +3350,55 @@
         <v>1</v>
       </c>
       <c r="AG9" s="3">
-        <v>0.3101035356521606</v>
+        <v>0.31010354</v>
       </c>
       <c r="AH9" s="3">
-        <v>0.3923474848270416</v>
+        <v>0.39234748</v>
       </c>
       <c r="AI9" s="3">
-        <v>0.8259280920028687</v>
+        <v>0.8259281000000001</v>
       </c>
       <c r="AJ9" s="3">
-        <v>0.06683070212602615</v>
+        <v>0.06683070000000001</v>
       </c>
       <c r="AK9" s="3">
-        <v>0.89606773853302</v>
+        <v>0.89606774</v>
       </c>
       <c r="AL9" s="3">
-        <v>0.3563961088657379</v>
+        <v>0.3563961</v>
       </c>
       <c r="AM9" s="3">
-        <v>0.6407724618911743</v>
+        <v>0.64077246</v>
       </c>
       <c r="AN9" s="3">
-        <v>0.7509437799453735</v>
+        <v>0.7509438000000001</v>
       </c>
       <c r="AO9" s="3">
-        <v>0.2986282408237457</v>
+        <v>0.29862824</v>
       </c>
       <c r="AP9" s="3">
-        <v>0.9887466430664062</v>
+        <v>0.98874664</v>
       </c>
       <c r="AQ9" s="3">
-        <v>0.999965488910675</v>
+        <v>0.9999655</v>
       </c>
       <c r="AR9" s="3">
-        <v>0.7102676630020142</v>
+        <v>0.71026766</v>
       </c>
       <c r="AS9" s="3">
-        <v>0.9408232569694519</v>
+        <v>0.9408232600000001</v>
       </c>
       <c r="AT9" s="3">
-        <v>0.8539096117019653</v>
+        <v>0.8539096</v>
       </c>
       <c r="AU9" s="3">
-        <v>-4.659994602203369</v>
+        <v>-4.6599946</v>
       </c>
       <c r="AV9" s="3">
-        <v>99.01403045654297</v>
+        <v>99.01403000000001</v>
       </c>
       <c r="AW9" s="3">
-        <v>5.339962959289551</v>
+        <v>5.339963</v>
       </c>
       <c r="AX9" s="3">
         <v>441.8900000000002</v>
@@ -3466,7 +3466,7 @@
         <v>5.442375258869468</v>
       </c>
       <c r="L10" s="3">
-        <v>0.9612163861567087</v>
+        <v>0.9612163861567088</v>
       </c>
       <c r="M10" s="3">
         <v>0.4573929864232385</v>
@@ -3513,13 +3513,13 @@
         </is>
       </c>
       <c r="AA10" s="3">
-        <v>63.14249801635742</v>
+        <v>63.142498</v>
       </c>
       <c r="AB10" s="3">
-        <v>59.44232940673828</v>
+        <v>59.44233</v>
       </c>
       <c r="AC10" s="3">
-        <v>40.98332977294922</v>
+        <v>40.98333</v>
       </c>
       <c r="AD10" s="3">
         <v>0</v>
@@ -3531,55 +3531,55 @@
         <v>0</v>
       </c>
       <c r="AG10" s="3">
-        <v>0.4299601018428802</v>
+        <v>0.4299601</v>
       </c>
       <c r="AH10" s="3">
-        <v>0.568150520324707</v>
+        <v>0.5681505</v>
       </c>
       <c r="AI10" s="3">
-        <v>0.7690213322639465</v>
+        <v>0.7690213299999999</v>
       </c>
       <c r="AJ10" s="3">
-        <v>0.1154319271445274</v>
+        <v>0.11543193</v>
       </c>
       <c r="AK10" s="3">
-        <v>0.962266743183136</v>
+        <v>0.96226674</v>
       </c>
       <c r="AL10" s="3">
-        <v>0.2106578052043915</v>
+        <v>0.2106578</v>
       </c>
       <c r="AM10" s="3">
-        <v>0.5720455050468445</v>
+        <v>0.5720455</v>
       </c>
       <c r="AN10" s="3">
-        <v>0.6004520654678345</v>
+        <v>0.60045207</v>
       </c>
       <c r="AO10" s="3">
-        <v>0.4409490525722504</v>
+        <v>0.44094905</v>
       </c>
       <c r="AP10" s="3">
-        <v>0.9696972966194153</v>
+        <v>0.9696973</v>
       </c>
       <c r="AQ10" s="3">
-        <v>0.999884307384491</v>
+        <v>0.9998842999999999</v>
       </c>
       <c r="AR10" s="3">
-        <v>0.7959489226341248</v>
+        <v>0.7959489</v>
       </c>
       <c r="AS10" s="3">
-        <v>0.9459794759750366</v>
+        <v>0.9459795</v>
       </c>
       <c r="AT10" s="3">
-        <v>0.90886390209198</v>
+        <v>0.9088638999999999</v>
       </c>
       <c r="AU10" s="3">
-        <v>-4.826195240020752</v>
+        <v>-4.8261952</v>
       </c>
       <c r="AV10" s="3">
-        <v>94.99932098388672</v>
+        <v>94.99932</v>
       </c>
       <c r="AW10" s="3">
-        <v>9.767364501953125</v>
+        <v>9.767364499999999</v>
       </c>
       <c r="AX10" s="3">
         <v>436.5120000000002</v>
@@ -3594,7 +3594,7 @@
         <v>4</v>
       </c>
       <c r="BB10" s="3">
-        <v>3.485622209764999</v>
+        <v>3.485622209765</v>
       </c>
       <c r="BC10" s="3">
         <v>0.7238197544705556</v>
@@ -3694,13 +3694,13 @@
         </is>
       </c>
       <c r="AA11" s="3">
-        <v>67.93006134033203</v>
+        <v>67.93006</v>
       </c>
       <c r="AB11" s="3">
-        <v>55.20512771606445</v>
+        <v>55.205128</v>
       </c>
       <c r="AC11" s="3">
-        <v>40.69406127929688</v>
+        <v>40.69406</v>
       </c>
       <c r="AD11" s="3">
         <v>0</v>
@@ -3712,55 +3712,55 @@
         <v>0</v>
       </c>
       <c r="AG11" s="3">
-        <v>0.2426725178956985</v>
+        <v>0.24267252</v>
       </c>
       <c r="AH11" s="3">
-        <v>0.5274170637130737</v>
+        <v>0.52741706</v>
       </c>
       <c r="AI11" s="3">
-        <v>0.8195544481277466</v>
+        <v>0.81955445</v>
       </c>
       <c r="AJ11" s="3">
-        <v>0.05707133933901787</v>
+        <v>0.05707134</v>
       </c>
       <c r="AK11" s="3">
-        <v>0.9460126757621765</v>
+        <v>0.9460127</v>
       </c>
       <c r="AL11" s="3">
-        <v>0.3255795240402222</v>
+        <v>0.32557952</v>
       </c>
       <c r="AM11" s="3">
-        <v>0.6021593809127808</v>
+        <v>0.6021594</v>
       </c>
       <c r="AN11" s="3">
-        <v>0.7146463990211487</v>
+        <v>0.7146464</v>
       </c>
       <c r="AO11" s="3">
-        <v>0.2755510210990906</v>
+        <v>0.27555102</v>
       </c>
       <c r="AP11" s="3">
-        <v>0.9880801439285278</v>
+        <v>0.98808014</v>
       </c>
       <c r="AQ11" s="3">
-        <v>0.9999575614929199</v>
+        <v>0.99995756</v>
       </c>
       <c r="AR11" s="3">
-        <v>0.7738900780677795</v>
+        <v>0.7738901</v>
       </c>
       <c r="AS11" s="3">
-        <v>0.9560348391532898</v>
+        <v>0.9560348400000001</v>
       </c>
       <c r="AT11" s="3">
-        <v>0.9067276120185852</v>
+        <v>0.9067276</v>
       </c>
       <c r="AU11" s="3">
-        <v>-4.787168979644775</v>
+        <v>-4.787169</v>
       </c>
       <c r="AV11" s="3">
-        <v>100.1134414672852</v>
+        <v>100.11344</v>
       </c>
       <c r="AW11" s="3">
-        <v>7.336748600006104</v>
+        <v>7.3367486</v>
       </c>
       <c r="AX11" s="3">
         <v>446.5510000000002</v>
@@ -3846,7 +3846,7 @@
         <v>0.5761692979434486</v>
       </c>
       <c r="R12" s="3">
-        <v>1.285738747074785</v>
+        <v>1.285738747074784</v>
       </c>
       <c r="S12" s="3">
         <v>233.2042065343045</v>
@@ -3875,13 +3875,13 @@
         </is>
       </c>
       <c r="AA12" s="3">
-        <v>50.03407669067383</v>
+        <v>50.034077</v>
       </c>
       <c r="AB12" s="3">
-        <v>47.67665481567383</v>
+        <v>47.676655</v>
       </c>
       <c r="AC12" s="3">
-        <v>41.62461471557617</v>
+        <v>41.624615</v>
       </c>
       <c r="AD12" s="3">
         <v>0</v>
@@ -3893,55 +3893,55 @@
         <v>0</v>
       </c>
       <c r="AG12" s="3">
-        <v>0.2527405619621277</v>
+        <v>0.25274056</v>
       </c>
       <c r="AH12" s="3">
-        <v>0.4688826203346252</v>
+        <v>0.46888262</v>
       </c>
       <c r="AI12" s="3">
-        <v>0.8351690173149109</v>
+        <v>0.8351690000000001</v>
       </c>
       <c r="AJ12" s="3">
-        <v>0.04883063584566116</v>
+        <v>0.048830636</v>
       </c>
       <c r="AK12" s="3">
-        <v>0.9386070370674133</v>
+        <v>0.9386070399999999</v>
       </c>
       <c r="AL12" s="3">
-        <v>0.3703396916389465</v>
+        <v>0.3703397</v>
       </c>
       <c r="AM12" s="3">
-        <v>0.6521977186203003</v>
+        <v>0.6521977</v>
       </c>
       <c r="AN12" s="3">
-        <v>0.7791668772697449</v>
+        <v>0.7791669</v>
       </c>
       <c r="AO12" s="3">
-        <v>0.2660718858242035</v>
+        <v>0.2660719</v>
       </c>
       <c r="AP12" s="3">
-        <v>0.9907934069633484</v>
+        <v>0.9907934</v>
       </c>
       <c r="AQ12" s="3">
-        <v>0.9999765157699585</v>
+        <v>0.9999765</v>
       </c>
       <c r="AR12" s="3">
-        <v>0.7638530731201172</v>
+        <v>0.7638531</v>
       </c>
       <c r="AS12" s="3">
-        <v>0.9541949033737183</v>
+        <v>0.9541949</v>
       </c>
       <c r="AT12" s="3">
-        <v>0.8792738914489746</v>
+        <v>0.8792739000000001</v>
       </c>
       <c r="AU12" s="3">
-        <v>-4.85697603225708</v>
+        <v>-4.856976</v>
       </c>
       <c r="AV12" s="3">
-        <v>99.01522064208984</v>
+        <v>99.01522</v>
       </c>
       <c r="AW12" s="3">
-        <v>8.199435234069824</v>
+        <v>8.199434999999999</v>
       </c>
       <c r="AX12" s="3">
         <v>432.5240000000002</v>
@@ -4021,7 +4021,7 @@
         <v>76.0808612751983</v>
       </c>
       <c r="P13" s="3">
-        <v>4.797356000773195</v>
+        <v>4.797356000773196</v>
       </c>
       <c r="Q13" s="3">
         <v>0.6027867767415637</v>
@@ -4033,7 +4033,7 @@
         <v>242.1620484371657</v>
       </c>
       <c r="T13" s="3">
-        <v>3.61589391835973</v>
+        <v>3.615893918359729</v>
       </c>
       <c r="U13" s="3">
         <v>5.97881808318666</v>
@@ -4056,13 +4056,13 @@
         </is>
       </c>
       <c r="AA13" s="3">
-        <v>59.47089767456055</v>
+        <v>59.470898</v>
       </c>
       <c r="AB13" s="3">
-        <v>57.21721267700195</v>
+        <v>57.217213</v>
       </c>
       <c r="AC13" s="3">
-        <v>40.80252838134766</v>
+        <v>40.80253</v>
       </c>
       <c r="AD13" s="3">
         <v>0</v>
@@ -4074,55 +4074,55 @@
         <v>0</v>
       </c>
       <c r="AG13" s="3">
-        <v>0.1844686567783356</v>
+        <v>0.18446866</v>
       </c>
       <c r="AH13" s="3">
-        <v>0.4202435612678528</v>
+        <v>0.42024356</v>
       </c>
       <c r="AI13" s="3">
-        <v>0.8358315229415894</v>
+        <v>0.8358314999999999</v>
       </c>
       <c r="AJ13" s="3">
-        <v>0.04515016824007034</v>
+        <v>0.04515017</v>
       </c>
       <c r="AK13" s="3">
-        <v>0.9386307597160339</v>
+        <v>0.93863076</v>
       </c>
       <c r="AL13" s="3">
-        <v>0.4181107878684998</v>
+        <v>0.4181108</v>
       </c>
       <c r="AM13" s="3">
-        <v>0.7442827224731445</v>
+        <v>0.7442827</v>
       </c>
       <c r="AN13" s="3">
-        <v>0.8617993593215942</v>
+        <v>0.86179936</v>
       </c>
       <c r="AO13" s="3">
-        <v>0.2975649237632751</v>
+        <v>0.29756492</v>
       </c>
       <c r="AP13" s="3">
-        <v>0.9936869740486145</v>
+        <v>0.993687</v>
       </c>
       <c r="AQ13" s="3">
-        <v>0.9999872446060181</v>
+        <v>0.9999872400000001</v>
       </c>
       <c r="AR13" s="3">
-        <v>0.7217900156974792</v>
+        <v>0.72179</v>
       </c>
       <c r="AS13" s="3">
-        <v>0.957022488117218</v>
+        <v>0.9570225</v>
       </c>
       <c r="AT13" s="3">
-        <v>0.9055355191230774</v>
+        <v>0.9055355</v>
       </c>
       <c r="AU13" s="3">
-        <v>-4.767285823822021</v>
+        <v>-4.767286</v>
       </c>
       <c r="AV13" s="3">
-        <v>101.1879043579102</v>
+        <v>101.187904</v>
       </c>
       <c r="AW13" s="3">
-        <v>5.748512268066406</v>
+        <v>5.7485123</v>
       </c>
       <c r="AX13" s="3">
         <v>432.5240000000002</v>
@@ -4237,13 +4237,13 @@
         </is>
       </c>
       <c r="AA14" s="3">
-        <v>48.67279434204102</v>
+        <v>48.672794</v>
       </c>
       <c r="AB14" s="3">
-        <v>50.2684326171875</v>
+        <v>50.268433</v>
       </c>
       <c r="AC14" s="3">
-        <v>44.13649749755859</v>
+        <v>44.136497</v>
       </c>
       <c r="AD14" s="3">
         <v>0</v>
@@ -4255,55 +4255,55 @@
         <v>0</v>
       </c>
       <c r="AG14" s="3">
-        <v>0.5435410737991333</v>
+        <v>0.5435411</v>
       </c>
       <c r="AH14" s="3">
-        <v>0.5425915122032166</v>
+        <v>0.5425915</v>
       </c>
       <c r="AI14" s="3">
-        <v>0.7698615193367004</v>
+        <v>0.7698615</v>
       </c>
       <c r="AJ14" s="3">
-        <v>0.1706003993749619</v>
+        <v>0.1706004</v>
       </c>
       <c r="AK14" s="3">
-        <v>0.9306700825691223</v>
+        <v>0.9306700999999999</v>
       </c>
       <c r="AL14" s="3">
-        <v>0.2514248788356781</v>
+        <v>0.25142488</v>
       </c>
       <c r="AM14" s="3">
-        <v>0.5852470397949219</v>
+        <v>0.5852470400000001</v>
       </c>
       <c r="AN14" s="3">
-        <v>0.639957070350647</v>
+        <v>0.6399570999999999</v>
       </c>
       <c r="AO14" s="3">
-        <v>0.4550451636314392</v>
+        <v>0.45504516</v>
       </c>
       <c r="AP14" s="3">
-        <v>0.9392004013061523</v>
+        <v>0.9392004</v>
       </c>
       <c r="AQ14" s="3">
-        <v>0.9997575879096985</v>
+        <v>0.9997576</v>
       </c>
       <c r="AR14" s="3">
-        <v>0.7301642298698425</v>
+        <v>0.73016423</v>
       </c>
       <c r="AS14" s="3">
-        <v>0.914487361907959</v>
+        <v>0.91448736</v>
       </c>
       <c r="AT14" s="3">
-        <v>0.8953701853752136</v>
+        <v>0.8953702</v>
       </c>
       <c r="AU14" s="3">
-        <v>-4.771430492401123</v>
+        <v>-4.7714305</v>
       </c>
       <c r="AV14" s="3">
-        <v>97.80867004394531</v>
+        <v>97.80867000000001</v>
       </c>
       <c r="AW14" s="3">
-        <v>9.259222984313965</v>
+        <v>9.259223</v>
       </c>
       <c r="AX14" s="3">
         <v>419.5050000000002</v>
@@ -4380,7 +4380,7 @@
         <v>14.9370461103721</v>
       </c>
       <c r="O15" s="3">
-        <v>9.749179286565441</v>
+        <v>9.74917928656544</v>
       </c>
       <c r="P15" s="3">
         <v>4.937192743725992</v>
@@ -4418,13 +4418,13 @@
         </is>
       </c>
       <c r="AA15" s="3">
-        <v>12.38687324523926</v>
+        <v>12.386873</v>
       </c>
       <c r="AB15" s="3">
-        <v>28.63481140136719</v>
+        <v>28.634811</v>
       </c>
       <c r="AC15" s="3">
-        <v>41.37298583984375</v>
+        <v>41.372986</v>
       </c>
       <c r="AD15" s="3">
         <v>0</v>
@@ -4436,55 +4436,55 @@
         <v>0</v>
       </c>
       <c r="AG15" s="3">
-        <v>0.1577767729759216</v>
+        <v>0.15777677</v>
       </c>
       <c r="AH15" s="3">
-        <v>0.5154687166213989</v>
+        <v>0.5154687</v>
       </c>
       <c r="AI15" s="3">
-        <v>0.3734657168388367</v>
+        <v>0.37346572</v>
       </c>
       <c r="AJ15" s="3">
-        <v>0.09895943105220795</v>
+        <v>0.09895943</v>
       </c>
       <c r="AK15" s="3">
-        <v>0.9235855340957642</v>
+        <v>0.92358553</v>
       </c>
       <c r="AL15" s="3">
-        <v>0.05056566745042801</v>
+        <v>0.050565667</v>
       </c>
       <c r="AM15" s="3">
-        <v>0.1717598587274551</v>
+        <v>0.17175986</v>
       </c>
       <c r="AN15" s="3">
-        <v>0.1719331741333008</v>
+        <v>0.17193317</v>
       </c>
       <c r="AO15" s="3">
-        <v>0.4868618547916412</v>
+        <v>0.48686185</v>
       </c>
       <c r="AP15" s="3">
-        <v>0.6581208109855652</v>
+        <v>0.6581208</v>
       </c>
       <c r="AQ15" s="3">
-        <v>0.9986150860786438</v>
+        <v>0.9986151</v>
       </c>
       <c r="AR15" s="3">
-        <v>0.7258269190788269</v>
+        <v>0.7258269000000001</v>
       </c>
       <c r="AS15" s="3">
-        <v>0.8411421775817871</v>
+        <v>0.8411422</v>
       </c>
       <c r="AT15" s="3">
-        <v>0.7036874294281006</v>
+        <v>0.7036874</v>
       </c>
       <c r="AU15" s="3">
-        <v>-4.742566585540771</v>
+        <v>-4.7425666</v>
       </c>
       <c r="AV15" s="3">
-        <v>86.36440277099609</v>
+        <v>86.3644</v>
       </c>
       <c r="AW15" s="3">
-        <v>11.66602993011475</v>
+        <v>11.66603</v>
       </c>
       <c r="AX15" s="3">
         <v>411.4960000000001</v>
@@ -4552,7 +4552,7 @@
         <v>5.394846103109279</v>
       </c>
       <c r="L16" s="3">
-        <v>0.9925874224306221</v>
+        <v>0.992587422430622</v>
       </c>
       <c r="M16" s="3">
         <v>0.4652062971367035</v>
@@ -4599,13 +4599,13 @@
         </is>
       </c>
       <c r="AA16" s="3">
-        <v>44.02022171020508</v>
+        <v>44.02022</v>
       </c>
       <c r="AB16" s="3">
-        <v>44.23410034179688</v>
+        <v>44.2341</v>
       </c>
       <c r="AC16" s="3">
-        <v>52.36737823486328</v>
+        <v>52.36738</v>
       </c>
       <c r="AD16" s="3">
         <v>0</v>
@@ -4617,55 +4617,55 @@
         <v>0</v>
       </c>
       <c r="AG16" s="3">
-        <v>0.4552529752254486</v>
+        <v>0.45525298</v>
       </c>
       <c r="AH16" s="3">
-        <v>0.5652529001235962</v>
+        <v>0.5652528999999999</v>
       </c>
       <c r="AI16" s="3">
-        <v>0.7355195283889771</v>
+        <v>0.7355195</v>
       </c>
       <c r="AJ16" s="3">
-        <v>0.1541751474142075</v>
+        <v>0.15417515</v>
       </c>
       <c r="AK16" s="3">
-        <v>0.9497561454772949</v>
+        <v>0.94975615</v>
       </c>
       <c r="AL16" s="3">
-        <v>0.2399992942810059</v>
+        <v>0.2399993</v>
       </c>
       <c r="AM16" s="3">
-        <v>0.5585464835166931</v>
+        <v>0.5585464999999999</v>
       </c>
       <c r="AN16" s="3">
-        <v>0.5594504475593567</v>
+        <v>0.55945045</v>
       </c>
       <c r="AO16" s="3">
-        <v>0.504874587059021</v>
+        <v>0.5048746</v>
       </c>
       <c r="AP16" s="3">
-        <v>0.9398250579833984</v>
+        <v>0.93982506</v>
       </c>
       <c r="AQ16" s="3">
-        <v>0.9998273849487305</v>
+        <v>0.9998274</v>
       </c>
       <c r="AR16" s="3">
-        <v>0.7830619812011719</v>
+        <v>0.783062</v>
       </c>
       <c r="AS16" s="3">
-        <v>0.9360119104385376</v>
+        <v>0.9360119</v>
       </c>
       <c r="AT16" s="3">
-        <v>0.875612735748291</v>
+        <v>0.87561274</v>
       </c>
       <c r="AU16" s="3">
-        <v>-4.655711650848389</v>
+        <v>-4.6557117</v>
       </c>
       <c r="AV16" s="3">
-        <v>91.41233825683594</v>
+        <v>91.41234</v>
       </c>
       <c r="AW16" s="3">
-        <v>11.63228416442871</v>
+        <v>11.632284</v>
       </c>
       <c r="AX16" s="3">
         <v>424.4760000000001</v>
@@ -4739,7 +4739,7 @@
         <v>0.5538972903245317</v>
       </c>
       <c r="N17" s="3">
-        <v>52.85744973393292</v>
+        <v>52.85744973393293</v>
       </c>
       <c r="O17" s="3">
         <v>73.97049186169482</v>
@@ -4780,13 +4780,13 @@
         </is>
       </c>
       <c r="AA17" s="3">
-        <v>39.75581741333008</v>
+        <v>39.755817</v>
       </c>
       <c r="AB17" s="3">
-        <v>32.81678771972656</v>
+        <v>32.816788</v>
       </c>
       <c r="AC17" s="3">
-        <v>42.63826751708984</v>
+        <v>42.638268</v>
       </c>
       <c r="AD17" s="3">
         <v>0</v>
@@ -4798,55 +4798,55 @@
         <v>0</v>
       </c>
       <c r="AG17" s="3">
-        <v>0.3349597454071045</v>
+        <v>0.33495975</v>
       </c>
       <c r="AH17" s="3">
-        <v>0.4971658289432526</v>
+        <v>0.49716583</v>
       </c>
       <c r="AI17" s="3">
-        <v>0.8305774927139282</v>
+        <v>0.8305775</v>
       </c>
       <c r="AJ17" s="3">
-        <v>0.05206187441945076</v>
+        <v>0.052061874</v>
       </c>
       <c r="AK17" s="3">
-        <v>0.9213895797729492</v>
+        <v>0.9213896</v>
       </c>
       <c r="AL17" s="3">
-        <v>0.2205078303813934</v>
+        <v>0.22050783</v>
       </c>
       <c r="AM17" s="3">
-        <v>0.4619075357913971</v>
+        <v>0.46190754</v>
       </c>
       <c r="AN17" s="3">
-        <v>0.5620790719985962</v>
+        <v>0.5620791000000001</v>
       </c>
       <c r="AO17" s="3">
-        <v>0.1509415209293365</v>
+        <v>0.15094152</v>
       </c>
       <c r="AP17" s="3">
-        <v>0.957487940788269</v>
+        <v>0.95748794</v>
       </c>
       <c r="AQ17" s="3">
-        <v>0.9998504519462585</v>
+        <v>0.9998504499999999</v>
       </c>
       <c r="AR17" s="3">
-        <v>0.8074136972427368</v>
+        <v>0.8074137</v>
       </c>
       <c r="AS17" s="3">
-        <v>0.9490911364555359</v>
+        <v>0.9490911400000001</v>
       </c>
       <c r="AT17" s="3">
-        <v>0.8077399134635925</v>
+        <v>0.8077399</v>
       </c>
       <c r="AU17" s="3">
-        <v>-4.965895175933838</v>
+        <v>-4.965895</v>
       </c>
       <c r="AV17" s="3">
-        <v>95.56562805175781</v>
+        <v>95.56563</v>
       </c>
       <c r="AW17" s="3">
-        <v>10.71188068389893</v>
+        <v>10.711881</v>
       </c>
       <c r="AX17" s="3">
         <v>417.5570000000001</v>
@@ -4961,13 +4961,13 @@
         </is>
       </c>
       <c r="AA18" s="3">
-        <v>28.59608459472656</v>
+        <v>28.596085</v>
       </c>
       <c r="AB18" s="3">
-        <v>28.57047080993652</v>
+        <v>28.57047</v>
       </c>
       <c r="AC18" s="3">
-        <v>49.00387573242188</v>
+        <v>49.003876</v>
       </c>
       <c r="AD18" s="3">
         <v>0</v>
@@ -4979,55 +4979,55 @@
         <v>0</v>
       </c>
       <c r="AG18" s="3">
-        <v>0.57878577709198</v>
+        <v>0.5787858</v>
       </c>
       <c r="AH18" s="3">
-        <v>0.5925208926200867</v>
+        <v>0.5925209</v>
       </c>
       <c r="AI18" s="3">
-        <v>0.761285126209259</v>
+        <v>0.7612851</v>
       </c>
       <c r="AJ18" s="3">
-        <v>0.1276874840259552</v>
+        <v>0.12768748</v>
       </c>
       <c r="AK18" s="3">
-        <v>0.961717426776886</v>
+        <v>0.9617173999999999</v>
       </c>
       <c r="AL18" s="3">
-        <v>0.3208934366703033</v>
+        <v>0.32089344</v>
       </c>
       <c r="AM18" s="3">
-        <v>0.6248059272766113</v>
+        <v>0.6248059</v>
       </c>
       <c r="AN18" s="3">
-        <v>0.6305137872695923</v>
+        <v>0.6305138</v>
       </c>
       <c r="AO18" s="3">
-        <v>0.5173318982124329</v>
+        <v>0.5173319</v>
       </c>
       <c r="AP18" s="3">
-        <v>0.9567925333976746</v>
+        <v>0.95679253</v>
       </c>
       <c r="AQ18" s="3">
-        <v>0.9998261332511902</v>
+        <v>0.99982613</v>
       </c>
       <c r="AR18" s="3">
-        <v>0.7589716911315918</v>
+        <v>0.7589717</v>
       </c>
       <c r="AS18" s="3">
-        <v>0.9170610308647156</v>
+        <v>0.9170610300000001</v>
       </c>
       <c r="AT18" s="3">
-        <v>0.8651493191719055</v>
+        <v>0.8651493</v>
       </c>
       <c r="AU18" s="3">
-        <v>-4.9692702293396</v>
+        <v>-4.96927</v>
       </c>
       <c r="AV18" s="3">
-        <v>95.90225219726562</v>
+        <v>95.90225</v>
       </c>
       <c r="AW18" s="3">
-        <v>11.49027442932129</v>
+        <v>11.490274</v>
       </c>
       <c r="AX18" s="3">
         <v>405.5020000000001</v>
@@ -5036,7 +5036,7 @@
         <v>3.435900000000002</v>
       </c>
       <c r="AZ18" s="3">
-        <v>0.3548017886240996</v>
+        <v>0.3548017886240995</v>
       </c>
       <c r="BA18" s="3">
         <v>4</v>
@@ -5116,7 +5116,7 @@
         <v>0.5610133228117108</v>
       </c>
       <c r="S19" s="3">
-        <v>372.1355666752823</v>
+        <v>372.1355666752824</v>
       </c>
       <c r="T19" s="3">
         <v>3.429298820511522</v>
@@ -5142,13 +5142,13 @@
         </is>
       </c>
       <c r="AA19" s="3">
-        <v>23.83349227905273</v>
+        <v>23.833492</v>
       </c>
       <c r="AB19" s="3">
-        <v>23.18177032470703</v>
+        <v>23.18177</v>
       </c>
       <c r="AC19" s="3">
-        <v>43.69765853881836</v>
+        <v>43.69766</v>
       </c>
       <c r="AD19" s="3">
         <v>0</v>
@@ -5160,55 +5160,55 @@
         <v>0</v>
       </c>
       <c r="AG19" s="3">
-        <v>0.6029369235038757</v>
+        <v>0.6029369</v>
       </c>
       <c r="AH19" s="3">
-        <v>0.5716692805290222</v>
+        <v>0.5716693</v>
       </c>
       <c r="AI19" s="3">
-        <v>0.759766697883606</v>
+        <v>0.7597667</v>
       </c>
       <c r="AJ19" s="3">
-        <v>0.1387667804956436</v>
+        <v>0.13876678</v>
       </c>
       <c r="AK19" s="3">
-        <v>0.9514781832695007</v>
+        <v>0.9514782000000001</v>
       </c>
       <c r="AL19" s="3">
-        <v>0.287363201379776</v>
+        <v>0.2873632</v>
       </c>
       <c r="AM19" s="3">
-        <v>0.5946284532546997</v>
+        <v>0.59462845</v>
       </c>
       <c r="AN19" s="3">
-        <v>0.5971899032592773</v>
+        <v>0.5971899000000001</v>
       </c>
       <c r="AO19" s="3">
-        <v>0.4520428776741028</v>
+        <v>0.45204288</v>
       </c>
       <c r="AP19" s="3">
-        <v>0.929568886756897</v>
+        <v>0.9295689</v>
       </c>
       <c r="AQ19" s="3">
-        <v>0.9996253848075867</v>
+        <v>0.9996254</v>
       </c>
       <c r="AR19" s="3">
-        <v>0.7747361660003662</v>
+        <v>0.7747361699999999</v>
       </c>
       <c r="AS19" s="3">
-        <v>0.9118067622184753</v>
+        <v>0.91180676</v>
       </c>
       <c r="AT19" s="3">
-        <v>0.8253988027572632</v>
+        <v>0.8253988</v>
       </c>
       <c r="AU19" s="3">
-        <v>-5.072853565216064</v>
+        <v>-5.0728536</v>
       </c>
       <c r="AV19" s="3">
-        <v>89.82477569580078</v>
+        <v>89.824776</v>
       </c>
       <c r="AW19" s="3">
-        <v>12.10881233215332</v>
+        <v>12.108812</v>
       </c>
       <c r="AX19" s="3">
         <v>405.5020000000001</v>
@@ -5323,13 +5323,13 @@
         </is>
       </c>
       <c r="AA20" s="3">
-        <v>38.19496536254883</v>
+        <v>38.194965</v>
       </c>
       <c r="AB20" s="3">
-        <v>46.53000640869141</v>
+        <v>46.530006</v>
       </c>
       <c r="AC20" s="3">
-        <v>52.06615447998047</v>
+        <v>52.066154</v>
       </c>
       <c r="AD20" s="3">
         <v>0</v>
@@ -5341,55 +5341,55 @@
         <v>0</v>
       </c>
       <c r="AG20" s="3">
-        <v>0.14383664727211</v>
+        <v>0.14383665</v>
       </c>
       <c r="AH20" s="3">
-        <v>0.2526366114616394</v>
+        <v>0.2526366</v>
       </c>
       <c r="AI20" s="3">
-        <v>0.7948338389396667</v>
+        <v>0.79483384</v>
       </c>
       <c r="AJ20" s="3">
-        <v>0.05038212984800339</v>
+        <v>0.05038213</v>
       </c>
       <c r="AK20" s="3">
-        <v>0.7190860509872437</v>
+        <v>0.71908605</v>
       </c>
       <c r="AL20" s="3">
-        <v>0.1829346120357513</v>
+        <v>0.18293461</v>
       </c>
       <c r="AM20" s="3">
-        <v>0.3825122117996216</v>
+        <v>0.3825122</v>
       </c>
       <c r="AN20" s="3">
-        <v>0.4498941898345947</v>
+        <v>0.4498942</v>
       </c>
       <c r="AO20" s="3">
-        <v>0.06359348446130753</v>
+        <v>0.06359348400000001</v>
       </c>
       <c r="AP20" s="3">
-        <v>0.8871018290519714</v>
+        <v>0.8871018000000001</v>
       </c>
       <c r="AQ20" s="3">
-        <v>0.9999326467514038</v>
+        <v>0.99993265</v>
       </c>
       <c r="AR20" s="3">
-        <v>0.8340276479721069</v>
+        <v>0.83402765</v>
       </c>
       <c r="AS20" s="3">
-        <v>0.9630118608474731</v>
+        <v>0.9630118600000001</v>
       </c>
       <c r="AT20" s="3">
-        <v>0.621238112449646</v>
+        <v>0.6212381</v>
       </c>
       <c r="AU20" s="3">
-        <v>-4.4007568359375</v>
+        <v>-4.400757</v>
       </c>
       <c r="AV20" s="3">
-        <v>87.47709655761719</v>
+        <v>87.47709999999999</v>
       </c>
       <c r="AW20" s="3">
-        <v>9.734237670898438</v>
+        <v>9.734238</v>
       </c>
       <c r="AX20" s="3">
         <v>411.4520000000001</v>
@@ -5457,7 +5457,7 @@
         <v>5.373032676973282</v>
       </c>
       <c r="L21" s="3">
-        <v>0.9412992172191981</v>
+        <v>0.941299217219198</v>
       </c>
       <c r="M21" s="3">
         <v>0.3091094834936228</v>
@@ -5504,13 +5504,13 @@
         </is>
       </c>
       <c r="AA21" s="3">
-        <v>44.03082275390625</v>
+        <v>44.030823</v>
       </c>
       <c r="AB21" s="3">
-        <v>52.285888671875</v>
+        <v>52.28589</v>
       </c>
       <c r="AC21" s="3">
-        <v>46.47859954833984</v>
+        <v>46.4786</v>
       </c>
       <c r="AD21" s="3">
         <v>0</v>
@@ -5522,55 +5522,55 @@
         <v>0</v>
       </c>
       <c r="AG21" s="3">
-        <v>0.148129865527153</v>
+        <v>0.14812987</v>
       </c>
       <c r="AH21" s="3">
-        <v>0.2408362925052643</v>
+        <v>0.24083629</v>
       </c>
       <c r="AI21" s="3">
-        <v>0.7796632647514343</v>
+        <v>0.77966326</v>
       </c>
       <c r="AJ21" s="3">
-        <v>0.04402393102645874</v>
+        <v>0.04402393</v>
       </c>
       <c r="AK21" s="3">
-        <v>0.6242526769638062</v>
+        <v>0.6242527</v>
       </c>
       <c r="AL21" s="3">
-        <v>0.1550628244876862</v>
+        <v>0.15506282</v>
       </c>
       <c r="AM21" s="3">
-        <v>0.2458717375993729</v>
+        <v>0.24587174</v>
       </c>
       <c r="AN21" s="3">
-        <v>0.2648356854915619</v>
+        <v>0.2648357</v>
       </c>
       <c r="AO21" s="3">
-        <v>0.03013482689857483</v>
+        <v>0.030134827</v>
       </c>
       <c r="AP21" s="3">
-        <v>0.7748693227767944</v>
+        <v>0.7748693</v>
       </c>
       <c r="AQ21" s="3">
-        <v>0.9999569058418274</v>
+        <v>0.9999569</v>
       </c>
       <c r="AR21" s="3">
-        <v>0.8821443319320679</v>
+        <v>0.88214433</v>
       </c>
       <c r="AS21" s="3">
-        <v>0.9609131813049316</v>
+        <v>0.9609132</v>
       </c>
       <c r="AT21" s="3">
-        <v>0.4224107265472412</v>
+        <v>0.42241073</v>
       </c>
       <c r="AU21" s="3">
-        <v>-4.425469398498535</v>
+        <v>-4.4254694</v>
       </c>
       <c r="AV21" s="3">
-        <v>90.94108581542969</v>
+        <v>90.941086</v>
       </c>
       <c r="AW21" s="3">
-        <v>7.257086277008057</v>
+        <v>7.2570863</v>
       </c>
       <c r="AX21" s="3">
         <v>367.3990000000001</v>
@@ -5685,13 +5685,13 @@
         </is>
       </c>
       <c r="AA22" s="3">
-        <v>46.68682098388672</v>
+        <v>46.68682</v>
       </c>
       <c r="AB22" s="3">
-        <v>46.50349807739258</v>
+        <v>46.503498</v>
       </c>
       <c r="AC22" s="3">
-        <v>40.06744003295898</v>
+        <v>40.06744</v>
       </c>
       <c r="AD22" s="3">
         <v>0</v>
@@ -5703,55 +5703,55 @@
         <v>0</v>
       </c>
       <c r="AG22" s="3">
-        <v>0.157486766576767</v>
+        <v>0.15748677</v>
       </c>
       <c r="AH22" s="3">
-        <v>0.357526034116745</v>
+        <v>0.35752603</v>
       </c>
       <c r="AI22" s="3">
-        <v>0.7977760434150696</v>
+        <v>0.79777604</v>
       </c>
       <c r="AJ22" s="3">
-        <v>0.05292393639683723</v>
+        <v>0.052923936</v>
       </c>
       <c r="AK22" s="3">
-        <v>0.86536705493927</v>
+        <v>0.86536705</v>
       </c>
       <c r="AL22" s="3">
-        <v>0.3862964510917664</v>
+        <v>0.38629645</v>
       </c>
       <c r="AM22" s="3">
-        <v>0.5458817481994629</v>
+        <v>0.5458817500000001</v>
       </c>
       <c r="AN22" s="3">
-        <v>0.6691522598266602</v>
+        <v>0.6691522600000001</v>
       </c>
       <c r="AO22" s="3">
-        <v>0.2068127393722534</v>
+        <v>0.20681274</v>
       </c>
       <c r="AP22" s="3">
-        <v>0.9757219552993774</v>
+        <v>0.97572196</v>
       </c>
       <c r="AQ22" s="3">
-        <v>0.9999698400497437</v>
+        <v>0.99996984</v>
       </c>
       <c r="AR22" s="3">
-        <v>0.7815946936607361</v>
+        <v>0.7815947</v>
       </c>
       <c r="AS22" s="3">
-        <v>0.9552289843559265</v>
+        <v>0.955229</v>
       </c>
       <c r="AT22" s="3">
-        <v>0.7651858925819397</v>
+        <v>0.7651859</v>
       </c>
       <c r="AU22" s="3">
-        <v>-4.575211524963379</v>
+        <v>-4.5752115</v>
       </c>
       <c r="AV22" s="3">
-        <v>96.03324890136719</v>
+        <v>96.03325</v>
       </c>
       <c r="AW22" s="3">
-        <v>5.789505958557129</v>
+        <v>5.789506</v>
       </c>
       <c r="AX22" s="3">
         <v>407.4450000000002</v>
@@ -5822,7 +5822,7 @@
         <v>0.938415746718696</v>
       </c>
       <c r="M23" s="3">
-        <v>0.2372612585811648</v>
+        <v>0.2372612585811647</v>
       </c>
       <c r="N23" s="3">
         <v>9.948615853378566</v>
@@ -5834,7 +5834,7 @@
         <v>5.061584253281304</v>
       </c>
       <c r="Q23" s="3">
-        <v>0.2372612585811648</v>
+        <v>0.2372612585811647</v>
       </c>
       <c r="R23" s="3">
         <v>2.974292526811678</v>
@@ -5849,7 +5849,7 @@
         <v>5.526616320100387</v>
       </c>
       <c r="V23" s="3">
-        <v>0.2372612585811648</v>
+        <v>0.2372612585811647</v>
       </c>
       <c r="W23" s="3">
         <v>3.314000000000002</v>
@@ -5858,7 +5858,7 @@
         <v>-5.017454811696665</v>
       </c>
       <c r="Y23" s="3">
-        <v>9.606057641337639E-06</v>
+        <v>9.60605764133764E-06</v>
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
@@ -5866,13 +5866,13 @@
         </is>
       </c>
       <c r="AA23" s="3">
-        <v>32.87833786010742</v>
+        <v>32.878338</v>
       </c>
       <c r="AB23" s="3">
-        <v>23.18183326721191</v>
+        <v>23.181833</v>
       </c>
       <c r="AC23" s="3">
-        <v>52.3669548034668</v>
+        <v>52.366955</v>
       </c>
       <c r="AD23" s="3">
         <v>0</v>
@@ -5884,55 +5884,55 @@
         <v>0</v>
       </c>
       <c r="AG23" s="3">
-        <v>0.1258585155010223</v>
+        <v>0.12585852</v>
       </c>
       <c r="AH23" s="3">
-        <v>0.2497570812702179</v>
+        <v>0.24975708</v>
       </c>
       <c r="AI23" s="3">
-        <v>0.8550773859024048</v>
+        <v>0.8550774</v>
       </c>
       <c r="AJ23" s="3">
-        <v>0.06400169432163239</v>
+        <v>0.064001694</v>
       </c>
       <c r="AK23" s="3">
-        <v>0.6612062454223633</v>
+        <v>0.66120625</v>
       </c>
       <c r="AL23" s="3">
-        <v>0.2865390479564667</v>
+        <v>0.28653905</v>
       </c>
       <c r="AM23" s="3">
-        <v>0.342566967010498</v>
+        <v>0.34256697</v>
       </c>
       <c r="AN23" s="3">
-        <v>0.4608744978904724</v>
+        <v>0.4608745</v>
       </c>
       <c r="AO23" s="3">
-        <v>0.05450470373034477</v>
+        <v>0.054504704</v>
       </c>
       <c r="AP23" s="3">
-        <v>0.763884425163269</v>
+        <v>0.7638844</v>
       </c>
       <c r="AQ23" s="3">
-        <v>0.9998586773872375</v>
+        <v>0.9998587</v>
       </c>
       <c r="AR23" s="3">
-        <v>0.882681667804718</v>
+        <v>0.88268167</v>
       </c>
       <c r="AS23" s="3">
-        <v>0.9536167979240417</v>
+        <v>0.9536168</v>
       </c>
       <c r="AT23" s="3">
-        <v>0.5413268804550171</v>
+        <v>0.5413269000000001</v>
       </c>
       <c r="AU23" s="3">
-        <v>-4.699678897857666</v>
+        <v>-4.699679</v>
       </c>
       <c r="AV23" s="3">
-        <v>97.27809143066406</v>
+        <v>97.27809000000001</v>
       </c>
       <c r="AW23" s="3">
-        <v>4.346566200256348</v>
+        <v>4.346566</v>
       </c>
       <c r="AX23" s="3">
         <v>401.3880000000001</v>
@@ -6000,10 +6000,10 @@
         <v>5.33313179110718</v>
       </c>
       <c r="L24" s="3">
-        <v>0.9537220237156057</v>
+        <v>0.9537220237156055</v>
       </c>
       <c r="M24" s="3">
-        <v>0.4635901738058765</v>
+        <v>0.4635901738058764</v>
       </c>
       <c r="N24" s="3">
         <v>14.14240057225329</v>
@@ -6015,10 +6015,10 @@
         <v>5.046277976284395</v>
       </c>
       <c r="Q24" s="3">
-        <v>0.4635901738058765</v>
+        <v>0.4635901738058764</v>
       </c>
       <c r="R24" s="3">
-        <v>1.109392646964843</v>
+        <v>1.109392646964842</v>
       </c>
       <c r="S24" s="3">
         <v>72.83812612751839</v>
@@ -6030,7 +6030,7 @@
         <v>5.954914716943912</v>
       </c>
       <c r="V24" s="3">
-        <v>0.4635901738058765</v>
+        <v>0.4635901738058764</v>
       </c>
       <c r="W24" s="3">
         <v>3.482800000000002</v>
@@ -6047,13 +6047,13 @@
         </is>
       </c>
       <c r="AA24" s="3">
-        <v>43.84062576293945</v>
+        <v>43.840626</v>
       </c>
       <c r="AB24" s="3">
-        <v>36.11913299560547</v>
+        <v>36.119133</v>
       </c>
       <c r="AC24" s="3">
-        <v>44.28573989868164</v>
+        <v>44.28574</v>
       </c>
       <c r="AD24" s="3">
         <v>0</v>
@@ -6065,55 +6065,55 @@
         <v>0</v>
       </c>
       <c r="AG24" s="3">
-        <v>0.4931285977363586</v>
+        <v>0.4931286</v>
       </c>
       <c r="AH24" s="3">
-        <v>0.2195391356945038</v>
+        <v>0.21953914</v>
       </c>
       <c r="AI24" s="3">
-        <v>0.9323638081550598</v>
+        <v>0.9323638</v>
       </c>
       <c r="AJ24" s="3">
-        <v>0.05992315337061882</v>
+        <v>0.059923153</v>
       </c>
       <c r="AK24" s="3">
-        <v>0.8766781091690063</v>
+        <v>0.8766781</v>
       </c>
       <c r="AL24" s="3">
-        <v>0.06521940231323242</v>
+        <v>0.0652194</v>
       </c>
       <c r="AM24" s="3">
-        <v>0.6295380592346191</v>
+        <v>0.62953806</v>
       </c>
       <c r="AN24" s="3">
-        <v>0.7626891136169434</v>
+        <v>0.7626891</v>
       </c>
       <c r="AO24" s="3">
-        <v>0.08053503930568695</v>
+        <v>0.08053504</v>
       </c>
       <c r="AP24" s="3">
-        <v>0.9835899472236633</v>
+        <v>0.98358995</v>
       </c>
       <c r="AQ24" s="3">
-        <v>0.9999303817749023</v>
+        <v>0.9999304</v>
       </c>
       <c r="AR24" s="3">
-        <v>0.7736954092979431</v>
+        <v>0.7736954</v>
       </c>
       <c r="AS24" s="3">
-        <v>0.9609892964363098</v>
+        <v>0.9609893</v>
       </c>
       <c r="AT24" s="3">
-        <v>0.925080418586731</v>
+        <v>0.9250804</v>
       </c>
       <c r="AU24" s="3">
-        <v>-4.878105163574219</v>
+        <v>-4.878105</v>
       </c>
       <c r="AV24" s="3">
-        <v>95.22494506835938</v>
+        <v>95.22494500000001</v>
       </c>
       <c r="AW24" s="3">
-        <v>10.51652240753174</v>
+        <v>10.516522</v>
       </c>
       <c r="AX24" s="3">
         <v>477.5650000000003</v>
@@ -6122,7 +6122,7 @@
         <v>3.482800000000002</v>
       </c>
       <c r="AZ24" s="3">
-        <v>0.2034588516904128</v>
+        <v>0.2034588516904127</v>
       </c>
       <c r="BA24" s="3">
         <v>4</v>
@@ -6228,13 +6228,13 @@
         </is>
       </c>
       <c r="AA25" s="3">
-        <v>21.76758003234863</v>
+        <v>21.76758</v>
       </c>
       <c r="AB25" s="3">
-        <v>12.32990837097168</v>
+        <v>12.329908</v>
       </c>
       <c r="AC25" s="3">
-        <v>60.55204391479492</v>
+        <v>60.552044</v>
       </c>
       <c r="AD25" s="3">
         <v>0</v>
@@ -6246,55 +6246,55 @@
         <v>0</v>
       </c>
       <c r="AG25" s="3">
-        <v>0.7771919965744019</v>
+        <v>0.777192</v>
       </c>
       <c r="AH25" s="3">
-        <v>0.6069221496582031</v>
+        <v>0.60692215</v>
       </c>
       <c r="AI25" s="3">
-        <v>0.7968754768371582</v>
+        <v>0.7968755</v>
       </c>
       <c r="AJ25" s="3">
-        <v>0.1225766912102699</v>
+        <v>0.12257669</v>
       </c>
       <c r="AK25" s="3">
-        <v>0.9637988805770874</v>
+        <v>0.9637989</v>
       </c>
       <c r="AL25" s="3">
-        <v>0.2132220268249512</v>
+        <v>0.21322203</v>
       </c>
       <c r="AM25" s="3">
-        <v>0.5798593759536743</v>
+        <v>0.5798594</v>
       </c>
       <c r="AN25" s="3">
-        <v>0.5465112924575806</v>
+        <v>0.5465113</v>
       </c>
       <c r="AO25" s="3">
-        <v>0.4234734177589417</v>
+        <v>0.42347342</v>
       </c>
       <c r="AP25" s="3">
-        <v>0.9334399104118347</v>
+        <v>0.9334399</v>
       </c>
       <c r="AQ25" s="3">
-        <v>0.9997305870056152</v>
+        <v>0.9997306</v>
       </c>
       <c r="AR25" s="3">
-        <v>0.734754204750061</v>
+        <v>0.7347542</v>
       </c>
       <c r="AS25" s="3">
-        <v>0.9173769950866699</v>
+        <v>0.917377</v>
       </c>
       <c r="AT25" s="3">
-        <v>0.8860563039779663</v>
+        <v>0.8860563</v>
       </c>
       <c r="AU25" s="3">
-        <v>-4.927274227142334</v>
+        <v>-4.927274</v>
       </c>
       <c r="AV25" s="3">
-        <v>96.48366546630859</v>
+        <v>96.483665</v>
       </c>
       <c r="AW25" s="3">
-        <v>11.95784282684326</v>
+        <v>11.957843</v>
       </c>
       <c r="AX25" s="3">
         <v>452.5340000000003</v>
@@ -6409,13 +6409,13 @@
         </is>
       </c>
       <c r="AA26" s="3">
-        <v>40.20576858520508</v>
+        <v>40.20577</v>
       </c>
       <c r="AB26" s="3">
-        <v>31.75322914123535</v>
+        <v>31.75323</v>
       </c>
       <c r="AC26" s="3">
-        <v>41.67095947265625</v>
+        <v>41.67096</v>
       </c>
       <c r="AD26" s="3">
         <v>0</v>
@@ -6427,55 +6427,55 @@
         <v>0</v>
       </c>
       <c r="AG26" s="3">
-        <v>0.4797840714454651</v>
+        <v>0.47978407</v>
       </c>
       <c r="AH26" s="3">
-        <v>0.2094463407993317</v>
+        <v>0.20944634</v>
       </c>
       <c r="AI26" s="3">
-        <v>0.9412010312080383</v>
+        <v>0.94120103</v>
       </c>
       <c r="AJ26" s="3">
-        <v>0.07010664045810699</v>
+        <v>0.07010664</v>
       </c>
       <c r="AK26" s="3">
-        <v>0.8604477047920227</v>
+        <v>0.8604477</v>
       </c>
       <c r="AL26" s="3">
-        <v>0.09299375861883163</v>
+        <v>0.09299375999999999</v>
       </c>
       <c r="AM26" s="3">
-        <v>0.6505425572395325</v>
+        <v>0.65054256</v>
       </c>
       <c r="AN26" s="3">
-        <v>0.7882941961288452</v>
+        <v>0.7882941999999999</v>
       </c>
       <c r="AO26" s="3">
-        <v>0.08256618678569794</v>
+        <v>0.08256619</v>
       </c>
       <c r="AP26" s="3">
-        <v>0.9790139198303223</v>
+        <v>0.9790139</v>
       </c>
       <c r="AQ26" s="3">
-        <v>0.9998863339424133</v>
+        <v>0.99988633</v>
       </c>
       <c r="AR26" s="3">
-        <v>0.7854633331298828</v>
+        <v>0.78546333</v>
       </c>
       <c r="AS26" s="3">
-        <v>0.9558399319648743</v>
+        <v>0.95583993</v>
       </c>
       <c r="AT26" s="3">
-        <v>0.9059475064277649</v>
+        <v>0.9059475</v>
       </c>
       <c r="AU26" s="3">
-        <v>-4.872025489807129</v>
+        <v>-4.8720255</v>
       </c>
       <c r="AV26" s="3">
-        <v>94.45332336425781</v>
+        <v>94.45332000000001</v>
       </c>
       <c r="AW26" s="3">
-        <v>9.490739822387695</v>
+        <v>9.490740000000001</v>
       </c>
       <c r="AX26" s="3">
         <v>463.5380000000002</v>
@@ -6590,13 +6590,13 @@
         </is>
       </c>
       <c r="AA27" s="3">
-        <v>27.08930969238281</v>
+        <v>27.08931</v>
       </c>
       <c r="AB27" s="3">
-        <v>20.42181777954102</v>
+        <v>20.421818</v>
       </c>
       <c r="AC27" s="3">
-        <v>50.60114288330078</v>
+        <v>50.601143</v>
       </c>
       <c r="AD27" s="3">
         <v>0</v>
@@ -6608,58 +6608,58 @@
         <v>0</v>
       </c>
       <c r="AG27" s="3">
-        <v>0.1081468015909195</v>
+        <v>0.1081468</v>
       </c>
       <c r="AH27" s="3">
-        <v>0.3498961925506592</v>
+        <v>0.3498962</v>
       </c>
       <c r="AI27" s="3">
-        <v>0.8508683443069458</v>
+        <v>0.85086834</v>
       </c>
       <c r="AJ27" s="3">
-        <v>0.04858250170946121</v>
+        <v>0.0485825</v>
       </c>
       <c r="AK27" s="3">
-        <v>0.8946163058280945</v>
+        <v>0.8946163</v>
       </c>
       <c r="AL27" s="3">
-        <v>0.277321994304657</v>
+        <v>0.277322</v>
       </c>
       <c r="AM27" s="3">
-        <v>0.6814662218093872</v>
+        <v>0.6814662</v>
       </c>
       <c r="AN27" s="3">
-        <v>0.8180170059204102</v>
+        <v>0.818017</v>
       </c>
       <c r="AO27" s="3">
-        <v>0.2221898287534714</v>
+        <v>0.22218983</v>
       </c>
       <c r="AP27" s="3">
-        <v>0.9871047139167786</v>
+        <v>0.9871046999999999</v>
       </c>
       <c r="AQ27" s="3">
-        <v>0.9999736547470093</v>
+        <v>0.99997365</v>
       </c>
       <c r="AR27" s="3">
-        <v>0.761349618434906</v>
+        <v>0.7613496</v>
       </c>
       <c r="AS27" s="3">
-        <v>0.9597161412239075</v>
+        <v>0.9597161400000001</v>
       </c>
       <c r="AT27" s="3">
-        <v>0.8450393676757812</v>
+        <v>0.84503937</v>
       </c>
       <c r="AU27" s="3">
-        <v>-4.713494300842285</v>
+        <v>-4.7134943</v>
       </c>
       <c r="AV27" s="3">
-        <v>97.13545227050781</v>
+        <v>97.13545000000001</v>
       </c>
       <c r="AW27" s="3">
-        <v>5.66744327545166</v>
+        <v>5.6674433</v>
       </c>
       <c r="AX27" s="3">
-        <v>472.4670000000003</v>
+        <v>472.4670000000002</v>
       </c>
       <c r="AY27" s="3">
         <v>3.439000000000003</v>
@@ -6745,7 +6745,7 @@
         <v>1.941800432483435</v>
       </c>
       <c r="S28" s="3">
-        <v>233.3246509673746</v>
+        <v>233.3246509673747</v>
       </c>
       <c r="T28" s="3">
         <v>3.63203937516447</v>
@@ -6771,13 +6771,13 @@
         </is>
       </c>
       <c r="AA28" s="3">
-        <v>17.60326957702637</v>
+        <v>17.60327</v>
       </c>
       <c r="AB28" s="3">
-        <v>15.00508594512939</v>
+        <v>15.005086</v>
       </c>
       <c r="AC28" s="3">
-        <v>60.3412971496582</v>
+        <v>60.341297</v>
       </c>
       <c r="AD28" s="3">
         <v>0</v>
@@ -6789,55 +6789,55 @@
         <v>0</v>
       </c>
       <c r="AG28" s="3">
-        <v>0.1759376227855682</v>
+        <v>0.17593762</v>
       </c>
       <c r="AH28" s="3">
-        <v>0.3225483298301697</v>
+        <v>0.32254833</v>
       </c>
       <c r="AI28" s="3">
-        <v>0.8475942611694336</v>
+        <v>0.84759426</v>
       </c>
       <c r="AJ28" s="3">
-        <v>0.04099674895405769</v>
+        <v>0.04099675</v>
       </c>
       <c r="AK28" s="3">
-        <v>0.850246250629425</v>
+        <v>0.85024625</v>
       </c>
       <c r="AL28" s="3">
-        <v>0.1296554058790207</v>
+        <v>0.1296554</v>
       </c>
       <c r="AM28" s="3">
-        <v>0.3709775507450104</v>
+        <v>0.37097755</v>
       </c>
       <c r="AN28" s="3">
-        <v>0.5289421677589417</v>
+        <v>0.52894217</v>
       </c>
       <c r="AO28" s="3">
-        <v>0.06528113782405853</v>
+        <v>0.06528114</v>
       </c>
       <c r="AP28" s="3">
-        <v>0.9636019468307495</v>
+        <v>0.96360195</v>
       </c>
       <c r="AQ28" s="3">
-        <v>0.999913215637207</v>
+        <v>0.9999131999999999</v>
       </c>
       <c r="AR28" s="3">
-        <v>0.8498846292495728</v>
+        <v>0.8498846</v>
       </c>
       <c r="AS28" s="3">
-        <v>0.9663764238357544</v>
+        <v>0.9663764</v>
       </c>
       <c r="AT28" s="3">
-        <v>0.7521975636482239</v>
+        <v>0.75219756</v>
       </c>
       <c r="AU28" s="3">
-        <v>-4.828359127044678</v>
+        <v>-4.828359</v>
       </c>
       <c r="AV28" s="3">
-        <v>92.74420928955078</v>
+        <v>92.74421</v>
       </c>
       <c r="AW28" s="3">
-        <v>11.26456642150879</v>
+        <v>11.264566</v>
       </c>
       <c r="AX28" s="3">
         <v>458.4840000000002</v>
@@ -6846,7 +6846,7 @@
         <v>3.423100000000002</v>
       </c>
       <c r="AZ28" s="3">
-        <v>0.4319787741095225</v>
+        <v>0.4319787741095224</v>
       </c>
       <c r="BA28" s="3">
         <v>4</v>
@@ -6914,7 +6914,7 @@
         <v>12.12319990519978</v>
       </c>
       <c r="O29" s="3">
-        <v>11.30303816696889</v>
+        <v>11.3030381669689</v>
       </c>
       <c r="P29" s="3">
         <v>5.04820129151144</v>
@@ -6952,13 +6952,13 @@
         </is>
       </c>
       <c r="AA29" s="3">
-        <v>24.0710563659668</v>
+        <v>24.071056</v>
       </c>
       <c r="AB29" s="3">
-        <v>23.20031547546387</v>
+        <v>23.200315</v>
       </c>
       <c r="AC29" s="3">
-        <v>48.26595687866211</v>
+        <v>48.265957</v>
       </c>
       <c r="AD29" s="3">
         <v>0</v>
@@ -6970,55 +6970,55 @@
         <v>0</v>
       </c>
       <c r="AG29" s="3">
-        <v>0.1182065010070801</v>
+        <v>0.1182065</v>
       </c>
       <c r="AH29" s="3">
-        <v>0.6393347382545471</v>
+        <v>0.63933474</v>
       </c>
       <c r="AI29" s="3">
-        <v>0.6041701436042786</v>
+        <v>0.60417014</v>
       </c>
       <c r="AJ29" s="3">
-        <v>0.1051495224237442</v>
+        <v>0.10514952</v>
       </c>
       <c r="AK29" s="3">
-        <v>0.9317499995231628</v>
+        <v>0.93175</v>
       </c>
       <c r="AL29" s="3">
-        <v>0.1908909529447556</v>
+        <v>0.19089095</v>
       </c>
       <c r="AM29" s="3">
-        <v>0.2398413866758347</v>
+        <v>0.23984139</v>
       </c>
       <c r="AN29" s="3">
-        <v>0.3507117033004761</v>
+        <v>0.3507117</v>
       </c>
       <c r="AO29" s="3">
-        <v>0.4600064158439636</v>
+        <v>0.46000642</v>
       </c>
       <c r="AP29" s="3">
-        <v>0.8681474924087524</v>
+        <v>0.8681475</v>
       </c>
       <c r="AQ29" s="3">
-        <v>0.9994595646858215</v>
+        <v>0.99945956</v>
       </c>
       <c r="AR29" s="3">
-        <v>0.7938547134399414</v>
+        <v>0.7938547</v>
       </c>
       <c r="AS29" s="3">
-        <v>0.875617504119873</v>
+        <v>0.8756175</v>
       </c>
       <c r="AT29" s="3">
-        <v>0.7619529962539673</v>
+        <v>0.761953</v>
       </c>
       <c r="AU29" s="3">
-        <v>-4.984997749328613</v>
+        <v>-4.9849977</v>
       </c>
       <c r="AV29" s="3">
-        <v>94.06256103515625</v>
+        <v>94.06256</v>
       </c>
       <c r="AW29" s="3">
-        <v>10.70411396026611</v>
+        <v>10.704114</v>
       </c>
       <c r="AX29" s="3">
         <v>420.5320000000001</v>
@@ -7133,13 +7133,13 @@
         </is>
       </c>
       <c r="AA30" s="3">
-        <v>28.10703659057617</v>
+        <v>28.107037</v>
       </c>
       <c r="AB30" s="3">
-        <v>28.69431686401367</v>
+        <v>28.694317</v>
       </c>
       <c r="AC30" s="3">
-        <v>48.72861099243164</v>
+        <v>48.72861</v>
       </c>
       <c r="AD30" s="3">
         <v>0</v>
@@ -7151,55 +7151,55 @@
         <v>0</v>
       </c>
       <c r="AG30" s="3">
-        <v>0.1811548471450806</v>
+        <v>0.18115485</v>
       </c>
       <c r="AH30" s="3">
-        <v>0.6515179872512817</v>
+        <v>0.651518</v>
       </c>
       <c r="AI30" s="3">
-        <v>0.6622465252876282</v>
+        <v>0.6622465</v>
       </c>
       <c r="AJ30" s="3">
-        <v>0.09961004555225372</v>
+        <v>0.09961004599999999</v>
       </c>
       <c r="AK30" s="3">
-        <v>0.9535791277885437</v>
+        <v>0.9535791</v>
       </c>
       <c r="AL30" s="3">
-        <v>0.1615898311138153</v>
+        <v>0.16158983</v>
       </c>
       <c r="AM30" s="3">
-        <v>0.2876680493354797</v>
+        <v>0.28766805</v>
       </c>
       <c r="AN30" s="3">
-        <v>0.4636885225772858</v>
+        <v>0.46368852</v>
       </c>
       <c r="AO30" s="3">
-        <v>0.4422608017921448</v>
+        <v>0.4422608</v>
       </c>
       <c r="AP30" s="3">
-        <v>0.9085427522659302</v>
+        <v>0.90854275</v>
       </c>
       <c r="AQ30" s="3">
-        <v>0.9986909627914429</v>
+        <v>0.99869096</v>
       </c>
       <c r="AR30" s="3">
-        <v>0.7246155738830566</v>
+        <v>0.7246156</v>
       </c>
       <c r="AS30" s="3">
-        <v>0.8257194757461548</v>
+        <v>0.8257195000000001</v>
       </c>
       <c r="AT30" s="3">
-        <v>0.8465056419372559</v>
+        <v>0.8465056399999999</v>
       </c>
       <c r="AU30" s="3">
-        <v>-5.251671314239502</v>
+        <v>-5.2516713</v>
       </c>
       <c r="AV30" s="3">
-        <v>95.00550842285156</v>
+        <v>95.00551</v>
       </c>
       <c r="AW30" s="3">
-        <v>11.14853477478027</v>
+        <v>11.148535</v>
       </c>
       <c r="AX30" s="3">
         <v>431.5840000000002</v>
@@ -7208,7 +7208,7 @@
         <v>3.406800000000001</v>
       </c>
       <c r="AZ30" s="3">
-        <v>0.3984526300599843</v>
+        <v>0.3984526300599842</v>
       </c>
       <c r="BA30" s="3">
         <v>4</v>
@@ -7285,7 +7285,7 @@
         <v>0.5417904351222217</v>
       </c>
       <c r="R31" s="3">
-        <v>1.974734185099057</v>
+        <v>1.974734185099056</v>
       </c>
       <c r="S31" s="3">
         <v>262.6196088127128</v>
@@ -7314,13 +7314,13 @@
         </is>
       </c>
       <c r="AA31" s="3">
-        <v>22.30717849731445</v>
+        <v>22.307178</v>
       </c>
       <c r="AB31" s="3">
-        <v>20.03717231750488</v>
+        <v>20.037172</v>
       </c>
       <c r="AC31" s="3">
-        <v>52.28086471557617</v>
+        <v>52.280865</v>
       </c>
       <c r="AD31" s="3">
         <v>0</v>
@@ -7332,55 +7332,55 @@
         <v>0</v>
       </c>
       <c r="AG31" s="3">
-        <v>0.1634544134140015</v>
+        <v>0.16345441</v>
       </c>
       <c r="AH31" s="3">
-        <v>0.69719398021698</v>
+        <v>0.697194</v>
       </c>
       <c r="AI31" s="3">
-        <v>0.6966174840927124</v>
+        <v>0.6966175</v>
       </c>
       <c r="AJ31" s="3">
-        <v>0.08969704806804657</v>
+        <v>0.08969705</v>
       </c>
       <c r="AK31" s="3">
-        <v>0.9630613327026367</v>
+        <v>0.96306133</v>
       </c>
       <c r="AL31" s="3">
-        <v>0.225770428776741</v>
+        <v>0.22577043</v>
       </c>
       <c r="AM31" s="3">
-        <v>0.3366061449050903</v>
+        <v>0.33660614</v>
       </c>
       <c r="AN31" s="3">
-        <v>0.5271130800247192</v>
+        <v>0.5271131</v>
       </c>
       <c r="AO31" s="3">
-        <v>0.4627063274383545</v>
+        <v>0.46270633</v>
       </c>
       <c r="AP31" s="3">
-        <v>0.9494125247001648</v>
+        <v>0.9494125</v>
       </c>
       <c r="AQ31" s="3">
-        <v>0.9993936419487</v>
+        <v>0.99939364</v>
       </c>
       <c r="AR31" s="3">
-        <v>0.7522884607315063</v>
+        <v>0.75228846</v>
       </c>
       <c r="AS31" s="3">
-        <v>0.8586667776107788</v>
+        <v>0.8586668</v>
       </c>
       <c r="AT31" s="3">
-        <v>0.8462157249450684</v>
+        <v>0.8462157</v>
       </c>
       <c r="AU31" s="3">
-        <v>-5.302098274230957</v>
+        <v>-5.3020983</v>
       </c>
       <c r="AV31" s="3">
-        <v>92.66982269287109</v>
+        <v>92.66982</v>
       </c>
       <c r="AW31" s="3">
-        <v>12.74984073638916</v>
+        <v>12.749841</v>
       </c>
       <c r="AX31" s="3">
         <v>431.5840000000002</v>
@@ -7454,7 +7454,7 @@
         <v>0.5470367383247328</v>
       </c>
       <c r="N32" s="3">
-        <v>51.24377626532831</v>
+        <v>51.24377626532832</v>
       </c>
       <c r="O32" s="3">
         <v>74.71041793425144</v>
@@ -7495,13 +7495,13 @@
         </is>
       </c>
       <c r="AA32" s="3">
-        <v>31.98368835449219</v>
+        <v>31.983688</v>
       </c>
       <c r="AB32" s="3">
-        <v>31.56573486328125</v>
+        <v>31.565735</v>
       </c>
       <c r="AC32" s="3">
-        <v>51.06867218017578</v>
+        <v>51.068672</v>
       </c>
       <c r="AD32" s="3">
         <v>0</v>
@@ -7513,55 +7513,55 @@
         <v>0</v>
       </c>
       <c r="AG32" s="3">
-        <v>0.1960595399141312</v>
+        <v>0.19605954</v>
       </c>
       <c r="AH32" s="3">
-        <v>0.6519123315811157</v>
+        <v>0.65191233</v>
       </c>
       <c r="AI32" s="3">
-        <v>0.636513352394104</v>
+        <v>0.63651335</v>
       </c>
       <c r="AJ32" s="3">
-        <v>0.1000093445181847</v>
+        <v>0.100009345</v>
       </c>
       <c r="AK32" s="3">
-        <v>0.9555538296699524</v>
+        <v>0.9555538</v>
       </c>
       <c r="AL32" s="3">
-        <v>0.2145792990922928</v>
+        <v>0.2145793</v>
       </c>
       <c r="AM32" s="3">
-        <v>0.2550626397132874</v>
+        <v>0.25506264</v>
       </c>
       <c r="AN32" s="3">
-        <v>0.3734226822853088</v>
+        <v>0.37342268</v>
       </c>
       <c r="AO32" s="3">
-        <v>0.4869077801704407</v>
+        <v>0.48690778</v>
       </c>
       <c r="AP32" s="3">
-        <v>0.8911203145980835</v>
+        <v>0.8911203</v>
       </c>
       <c r="AQ32" s="3">
-        <v>0.9990541338920593</v>
+        <v>0.99905413</v>
       </c>
       <c r="AR32" s="3">
-        <v>0.7657650113105774</v>
+        <v>0.765765</v>
       </c>
       <c r="AS32" s="3">
-        <v>0.8602112531661987</v>
+        <v>0.86021125</v>
       </c>
       <c r="AT32" s="3">
-        <v>0.8396522402763367</v>
+        <v>0.83965224</v>
       </c>
       <c r="AU32" s="3">
-        <v>-5.287175178527832</v>
+        <v>-5.287175</v>
       </c>
       <c r="AV32" s="3">
-        <v>93.912841796875</v>
+        <v>93.91284</v>
       </c>
       <c r="AW32" s="3">
-        <v>12.82140350341797</v>
+        <v>12.8214035</v>
       </c>
       <c r="AX32" s="3">
         <v>431.5840000000002</v>
@@ -7676,13 +7676,13 @@
         </is>
       </c>
       <c r="AA33" s="3">
-        <v>25.1324348449707</v>
+        <v>25.132435</v>
       </c>
       <c r="AB33" s="3">
-        <v>17.11425399780273</v>
+        <v>17.114254</v>
       </c>
       <c r="AC33" s="3">
-        <v>65.07199096679688</v>
+        <v>65.07199</v>
       </c>
       <c r="AD33" s="3">
         <v>0</v>
@@ -7694,55 +7694,55 @@
         <v>1</v>
       </c>
       <c r="AG33" s="3">
-        <v>0.8402185440063477</v>
+        <v>0.84021854</v>
       </c>
       <c r="AH33" s="3">
-        <v>0.5610002875328064</v>
+        <v>0.5610003</v>
       </c>
       <c r="AI33" s="3">
-        <v>0.8250879049301147</v>
+        <v>0.8250879</v>
       </c>
       <c r="AJ33" s="3">
-        <v>0.1387093365192413</v>
+        <v>0.13870934</v>
       </c>
       <c r="AK33" s="3">
-        <v>0.9534344673156738</v>
+        <v>0.95343447</v>
       </c>
       <c r="AL33" s="3">
-        <v>0.2219662219285965</v>
+        <v>0.22196622</v>
       </c>
       <c r="AM33" s="3">
-        <v>0.5726925730705261</v>
+        <v>0.5726926</v>
       </c>
       <c r="AN33" s="3">
-        <v>0.5306431651115417</v>
+        <v>0.5306431700000001</v>
       </c>
       <c r="AO33" s="3">
-        <v>0.3961922824382782</v>
+        <v>0.39619228</v>
       </c>
       <c r="AP33" s="3">
-        <v>0.9186362028121948</v>
+        <v>0.9186362</v>
       </c>
       <c r="AQ33" s="3">
-        <v>0.9995017051696777</v>
+        <v>0.9995017</v>
       </c>
       <c r="AR33" s="3">
-        <v>0.7318305373191833</v>
+        <v>0.73183054</v>
       </c>
       <c r="AS33" s="3">
-        <v>0.9001423716545105</v>
+        <v>0.9001424</v>
       </c>
       <c r="AT33" s="3">
-        <v>0.8343578577041626</v>
+        <v>0.83435786</v>
       </c>
       <c r="AU33" s="3">
-        <v>-4.990559577941895</v>
+        <v>-4.9905596</v>
       </c>
       <c r="AV33" s="3">
-        <v>96.46775054931641</v>
+        <v>96.46775</v>
       </c>
       <c r="AW33" s="3">
-        <v>12.70693111419678</v>
+        <v>12.706931</v>
       </c>
       <c r="AX33" s="3">
         <v>454.9620000000003</v>
@@ -7751,7 +7751,7 @@
         <v>3.237000000000001</v>
       </c>
       <c r="AZ33" s="3">
-        <v>0.1717996572987157</v>
+        <v>0.1717996572987156</v>
       </c>
       <c r="BA33" s="3">
         <v>4</v>
@@ -7810,7 +7810,7 @@
         <v>5.302380392493043</v>
       </c>
       <c r="L34" s="3">
-        <v>1.164451689027664</v>
+        <v>1.164451689027663</v>
       </c>
       <c r="M34" s="3">
         <v>0.7055939088529146</v>
@@ -7857,13 +7857,13 @@
         </is>
       </c>
       <c r="AA34" s="3">
-        <v>36.05014801025391</v>
+        <v>36.050148</v>
       </c>
       <c r="AB34" s="3">
-        <v>30.22350692749023</v>
+        <v>30.223507</v>
       </c>
       <c r="AC34" s="3">
-        <v>54.2916374206543</v>
+        <v>54.291637</v>
       </c>
       <c r="AD34" s="3">
         <v>0</v>
@@ -7875,55 +7875,55 @@
         <v>0</v>
       </c>
       <c r="AG34" s="3">
-        <v>0.4844598174095154</v>
+        <v>0.48445982</v>
       </c>
       <c r="AH34" s="3">
-        <v>0.5690391659736633</v>
+        <v>0.56903917</v>
       </c>
       <c r="AI34" s="3">
-        <v>0.8193802833557129</v>
+        <v>0.8193803</v>
       </c>
       <c r="AJ34" s="3">
-        <v>0.1135908514261246</v>
+        <v>0.11359085</v>
       </c>
       <c r="AK34" s="3">
-        <v>0.9744927287101746</v>
+        <v>0.9744927</v>
       </c>
       <c r="AL34" s="3">
-        <v>0.2221218794584274</v>
+        <v>0.22212188</v>
       </c>
       <c r="AM34" s="3">
-        <v>0.7059618830680847</v>
+        <v>0.7059619</v>
       </c>
       <c r="AN34" s="3">
-        <v>0.7573839426040649</v>
+        <v>0.75738394</v>
       </c>
       <c r="AO34" s="3">
-        <v>0.4451750218868256</v>
+        <v>0.44517502</v>
       </c>
       <c r="AP34" s="3">
-        <v>0.9823835492134094</v>
+        <v>0.98238355</v>
       </c>
       <c r="AQ34" s="3">
-        <v>0.9998828768730164</v>
+        <v>0.9998829</v>
       </c>
       <c r="AR34" s="3">
-        <v>0.7446204423904419</v>
+        <v>0.7446204400000001</v>
       </c>
       <c r="AS34" s="3">
-        <v>0.9404605031013489</v>
+        <v>0.9404605</v>
       </c>
       <c r="AT34" s="3">
-        <v>0.9413713216781616</v>
+        <v>0.9413713</v>
       </c>
       <c r="AU34" s="3">
-        <v>-5.038694381713867</v>
+        <v>-5.0386944</v>
       </c>
       <c r="AV34" s="3">
-        <v>94.14237213134766</v>
+        <v>94.14237</v>
       </c>
       <c r="AW34" s="3">
-        <v>14.30584239959717</v>
+        <v>14.305842</v>
       </c>
       <c r="AX34" s="3">
         <v>449.5550000000002</v>
@@ -7932,7 +7932,7 @@
         <v>3.452500000000001</v>
       </c>
       <c r="AZ34" s="3">
-        <v>0.2166721878325666</v>
+        <v>0.2166721878325665</v>
       </c>
       <c r="BA34" s="3">
         <v>4</v>
